--- a/InputData/elec/GBSC/Grid Battery Storage Capacities.xlsx
+++ b/InputData/elec/GBSC/Grid Battery Storage Capacities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\GBSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B76BDA5-6B6E-4B61-B1CD-00B7347D6B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B208FE68-64E5-4108-BF53-8E7FAC0EFDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1657,23 +1657,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
-    <col min="2" max="2" width="60.7265625" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1681,98 +1681,98 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="46" t="s">
         <v>185</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1000</v>
       </c>
@@ -1789,14 +1789,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AK114"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" customWidth="1"/>
-    <col min="2" max="2" width="45.7265625" customWidth="1"/>
+    <col min="1" max="1" width="32.140625" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
     <col min="38" max="38" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="10" t="s">
         <v>128</v>
       </c>
@@ -1903,8 +1903,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
@@ -1915,7 +1915,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="6" t="s">
         <v>4</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
@@ -1950,7 +1950,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
     </row>
-    <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
@@ -1958,12 +1958,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>11</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
         <v>12</v>
       </c>
@@ -2183,18 +2183,18 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>-1.4527999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>17</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>-1.2109E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>19</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>2.2502999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>8.456E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>23</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>-5.6340000000000001E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>25</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:37" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:37" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>27</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>0.123014</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>29</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>5.8900000000000003E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>31</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>2.3185000000000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>33</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>36</v>
       </c>
@@ -3437,12 +3437,12 @@
         <v>1.1344E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>39</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>-3.3660000000000001E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>41</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>-9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>44</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>-9.68E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>6.6000000000000005E-5</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>46</v>
       </c>
@@ -4120,12 +4120,12 @@
         <v>-4.06E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>48</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>49</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>50</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>51</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>52</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>54</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>55</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>56</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>57</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>58</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>60</v>
       </c>
@@ -5368,12 +5368,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="13" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>62</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>63</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>64</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>65</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>66</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>67</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>68</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>69</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>70</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>71</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>72</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>73</v>
       </c>
@@ -6729,12 +6729,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>75</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>76</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>77</v>
       </c>
@@ -7073,7 +7073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>78</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>79</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>80</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>81</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>82</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>83</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>84</v>
       </c>
@@ -7864,7 +7864,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>85</v>
       </c>
@@ -7977,12 +7977,12 @@
         <v>1.1053E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>88</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>-9.3640000000000008E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>89</v>
       </c>
@@ -8208,7 +8208,7 @@
         <v>-2.039E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>91</v>
       </c>
@@ -8321,7 +8321,7 @@
         <v>2.5253000000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>93</v>
       </c>
@@ -8434,7 +8434,7 @@
         <v>-7.0799999999999997E-4</v>
       </c>
     </row>
-    <row r="81" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>95</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>6.0502E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>96</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>4.0169999999999997E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>98</v>
       </c>
@@ -8773,7 +8773,7 @@
         <v>4.7788999999999998E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>99</v>
       </c>
@@ -8886,8 +8886,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="87" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="47" t="s">
         <v>101</v>
       </c>
@@ -8927,137 +8927,137 @@
       <c r="AJ87" s="47"/>
       <c r="AK87" s="47"/>
     </row>
-    <row r="88" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="8" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="8" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="94" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="8" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="96" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="8" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="8" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="8" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="8" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="8" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="8" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="8" t="s">
         <v>143</v>
       </c>
@@ -9073,14 +9073,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CCE644-1F6E-448D-BF65-99E32F75F792}">
   <dimension ref="A1:AG2837"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.453125" style="25" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="25" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="49" style="25" customWidth="1"/>
-    <col min="3" max="16384" width="9.1796875" style="25"/>
+    <col min="3" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="26" t="s">
         <v>174</v>
       </c>
@@ -9175,8 +9175,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="41" t="s">
         <v>3</v>
       </c>
@@ -9187,7 +9187,7 @@
       <c r="F3" s="41"/>
       <c r="G3" s="41"/>
     </row>
-    <row r="4" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="41" t="s">
         <v>4</v>
       </c>
@@ -9200,7 +9200,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="41" t="s">
         <v>6</v>
       </c>
@@ -9211,7 +9211,7 @@
       <c r="F5" s="41"/>
       <c r="G5" s="41"/>
     </row>
-    <row r="6" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="41" t="s">
         <v>7</v>
       </c>
@@ -9222,10 +9222,10 @@
       <c r="F6" s="41"/>
       <c r="G6" s="41"/>
     </row>
-    <row r="7" spans="1:33" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:33" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:33" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:33" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:33" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>8</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="26" t="s">
         <v>10</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="26"/>
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
@@ -9280,7 +9280,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
         <v>12</v>
       </c>
@@ -9378,18 +9378,18 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="31" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="31" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>15</v>
       </c>
@@ -9490,7 +9490,7 @@
         <v>-2.3927E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>17</v>
       </c>
@@ -9591,7 +9591,7 @@
         <v>-2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>19</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>1.8599000000000001E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>21</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>2.8872999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>23</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>-5.8170000000000001E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>25</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>27</v>
       </c>
@@ -10096,7 +10096,7 @@
         <v>6.9309999999999997E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
         <v>29</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>4.9199999999999999E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
         <v>31</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>3.2424000000000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>33</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="28" t="s">
         <v>36</v>
       </c>
@@ -10500,12 +10500,12 @@
         <v>1.7170999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="31" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
         <v>39</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>-5.385E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
         <v>41</v>
       </c>
@@ -10707,7 +10707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
         <v>43</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>-2.9E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
         <v>44</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
         <v>45</v>
       </c>
@@ -11010,7 +11010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" ht="12" x14ac:dyDescent="0.2">
       <c r="A34" s="28" t="s">
         <v>46</v>
       </c>
@@ -11111,13 +11111,13 @@
         <v>-5.3499999999999999E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="1:33" ht="12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:33" ht="12" x14ac:dyDescent="0.2">
       <c r="B36" s="31" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
         <v>48</v>
       </c>
@@ -11218,7 +11218,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
         <v>49</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
         <v>50</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
         <v>51</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
         <v>52</v>
       </c>
@@ -11622,7 +11622,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
         <v>54</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="28" t="s">
         <v>55</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
         <v>56</v>
       </c>
@@ -11925,7 +11925,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="28" t="s">
         <v>57</v>
       </c>
@@ -12026,7 +12026,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
         <v>58</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:33" ht="12" x14ac:dyDescent="0.2">
       <c r="A47" s="28" t="s">
         <v>60</v>
       </c>
@@ -12228,12 +12228,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" ht="12" x14ac:dyDescent="0.2">
       <c r="B48" s="31" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="28" t="s">
         <v>62</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
         <v>63</v>
       </c>
@@ -12435,7 +12435,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="28" t="s">
         <v>64</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
         <v>65</v>
       </c>
@@ -12637,7 +12637,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="28" t="s">
         <v>66</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
         <v>67</v>
       </c>
@@ -12839,7 +12839,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="28" t="s">
         <v>68</v>
       </c>
@@ -12940,7 +12940,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
         <v>69</v>
       </c>
@@ -13041,7 +13041,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="28" t="s">
         <v>70</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
         <v>71</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="28" t="s">
         <v>72</v>
       </c>
@@ -13344,7 +13344,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="28" t="s">
         <v>73</v>
       </c>
@@ -13445,12 +13445,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="31" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="28" t="s">
         <v>75</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
         <v>76</v>
       </c>
@@ -13652,7 +13652,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="28" t="s">
         <v>77</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
         <v>78</v>
       </c>
@@ -13854,7 +13854,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="28" t="s">
         <v>79</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
         <v>80</v>
       </c>
@@ -14056,7 +14056,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="28" t="s">
         <v>81</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
         <v>82</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="28" t="s">
         <v>83</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="28" t="s">
         <v>84</v>
       </c>
@@ -14460,8 +14460,8 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:33" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="28" t="s">
         <v>85</v>
       </c>
@@ -14562,12 +14562,12 @@
         <v>1.6822E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="31" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="28" t="s">
         <v>88</v>
       </c>
@@ -14668,7 +14668,7 @@
         <v>-5.5339999999999999E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
         <v>89</v>
       </c>
@@ -14769,7 +14769,7 @@
         <v>-6.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="28" t="s">
         <v>91</v>
       </c>
@@ -14870,7 +14870,7 @@
         <v>1.1887E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
         <v>93</v>
       </c>
@@ -14971,7 +14971,7 @@
         <v>5.5900000000000004E-4</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" s="28" t="s">
         <v>95</v>
       </c>
@@ -15072,7 +15072,7 @@
         <v>4.9362000000000003E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
         <v>96</v>
       </c>
@@ -15173,7 +15173,7 @@
         <v>1.895E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="28" t="s">
         <v>98</v>
       </c>
@@ -15274,7 +15274,7 @@
         <v>3.9856000000000003E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="28" t="s">
         <v>99</v>
       </c>
@@ -15375,133 +15375,133 @@
         <v>164</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="87" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:33" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="38" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="37" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="37" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="37" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="37" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:33" ht="12" x14ac:dyDescent="0.2">
       <c r="B92" s="37" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B93" s="37" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="37" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="37" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="37" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="97" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B97" s="37" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="98" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" s="37" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="99" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="37" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="100" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B100" s="37" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="101" spans="2:33" ht="12" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:33" ht="12" x14ac:dyDescent="0.2">
       <c r="B101" s="37" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="102" spans="2:33" ht="12" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:33" ht="12" x14ac:dyDescent="0.2">
       <c r="B102" s="37" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="103" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B103" s="37" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="104" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" s="37" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="105" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" s="37" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="106" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="37" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="107" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="37" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="108" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="37" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="109" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" s="37" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="110" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="37" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="111" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="37" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="112" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="48"/>
       <c r="C112" s="48"/>
       <c r="D112" s="48"/>
@@ -15535,16 +15535,16 @@
       <c r="AF112" s="48"/>
       <c r="AG112" s="48"/>
     </row>
-    <row r="141" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="12" x14ac:dyDescent="0.3"/>
-    <row r="308" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="308" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B308" s="48"/>
       <c r="C308" s="48"/>
       <c r="D308" s="48"/>
@@ -15578,7 +15578,7 @@
       <c r="AF308" s="48"/>
       <c r="AG308" s="48"/>
     </row>
-    <row r="511" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B511" s="48"/>
       <c r="C511" s="48"/>
       <c r="D511" s="48"/>
@@ -15612,7 +15612,7 @@
       <c r="AF511" s="48"/>
       <c r="AG511" s="48"/>
     </row>
-    <row r="712" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B712" s="48"/>
       <c r="C712" s="48"/>
       <c r="D712" s="48"/>
@@ -15646,7 +15646,7 @@
       <c r="AF712" s="48"/>
       <c r="AG712" s="48"/>
     </row>
-    <row r="887" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="887" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B887" s="48"/>
       <c r="C887" s="48"/>
       <c r="D887" s="48"/>
@@ -15680,7 +15680,7 @@
       <c r="AF887" s="48"/>
       <c r="AG887" s="48"/>
     </row>
-    <row r="1100" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1100" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1100" s="48"/>
       <c r="C1100" s="48"/>
       <c r="D1100" s="48"/>
@@ -15714,7 +15714,7 @@
       <c r="AF1100" s="48"/>
       <c r="AG1100" s="48"/>
     </row>
-    <row r="1227" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1227" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1227" s="48"/>
       <c r="C1227" s="48"/>
       <c r="D1227" s="48"/>
@@ -15748,7 +15748,7 @@
       <c r="AF1227" s="48"/>
       <c r="AG1227" s="48"/>
     </row>
-    <row r="1390" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1390" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1390" s="48"/>
       <c r="C1390" s="48"/>
       <c r="D1390" s="48"/>
@@ -15782,7 +15782,7 @@
       <c r="AF1390" s="48"/>
       <c r="AG1390" s="48"/>
     </row>
-    <row r="1502" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1502" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1502" s="48"/>
       <c r="C1502" s="48"/>
       <c r="D1502" s="48"/>
@@ -15816,7 +15816,7 @@
       <c r="AF1502" s="48"/>
       <c r="AG1502" s="48"/>
     </row>
-    <row r="1604" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1604" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1604" s="48"/>
       <c r="C1604" s="48"/>
       <c r="D1604" s="48"/>
@@ -15850,7 +15850,7 @@
       <c r="AF1604" s="48"/>
       <c r="AG1604" s="48"/>
     </row>
-    <row r="1698" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1698" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1698" s="48"/>
       <c r="C1698" s="48"/>
       <c r="D1698" s="48"/>
@@ -15884,7 +15884,7 @@
       <c r="AF1698" s="48"/>
       <c r="AG1698" s="48"/>
     </row>
-    <row r="1945" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1945" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1945" s="48"/>
       <c r="C1945" s="48"/>
       <c r="D1945" s="48"/>
@@ -15918,7 +15918,7 @@
       <c r="AF1945" s="48"/>
       <c r="AG1945" s="48"/>
     </row>
-    <row r="2031" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2031" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2031" s="48"/>
       <c r="C2031" s="48"/>
       <c r="D2031" s="48"/>
@@ -15952,7 +15952,7 @@
       <c r="AF2031" s="48"/>
       <c r="AG2031" s="48"/>
     </row>
-    <row r="2153" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2153" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2153" s="48"/>
       <c r="C2153" s="48"/>
       <c r="D2153" s="48"/>
@@ -15986,7 +15986,7 @@
       <c r="AF2153" s="48"/>
       <c r="AG2153" s="48"/>
     </row>
-    <row r="2317" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2317" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2317" s="48"/>
       <c r="C2317" s="48"/>
       <c r="D2317" s="48"/>
@@ -16020,7 +16020,7 @@
       <c r="AF2317" s="48"/>
       <c r="AG2317" s="48"/>
     </row>
-    <row r="2419" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2419" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2419" s="48"/>
       <c r="C2419" s="48"/>
       <c r="D2419" s="48"/>
@@ -16054,7 +16054,7 @@
       <c r="AF2419" s="48"/>
       <c r="AG2419" s="48"/>
     </row>
-    <row r="2509" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2509" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2509" s="48"/>
       <c r="C2509" s="48"/>
       <c r="D2509" s="48"/>
@@ -16088,7 +16088,7 @@
       <c r="AF2509" s="48"/>
       <c r="AG2509" s="48"/>
     </row>
-    <row r="2598" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2598" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2598" s="48"/>
       <c r="C2598" s="48"/>
       <c r="D2598" s="48"/>
@@ -16122,7 +16122,7 @@
       <c r="AF2598" s="48"/>
       <c r="AG2598" s="48"/>
     </row>
-    <row r="2719" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2719" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2719" s="48"/>
       <c r="C2719" s="48"/>
       <c r="D2719" s="48"/>
@@ -16156,7 +16156,7 @@
       <c r="AF2719" s="48"/>
       <c r="AG2719" s="48"/>
     </row>
-    <row r="2837" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2837" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2837" s="48"/>
       <c r="C2837" s="48"/>
       <c r="D2837" s="48"/>
@@ -16224,13 +16224,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>124</v>
       </c>
@@ -16238,7 +16238,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>127</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>3968</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
     </row>
   </sheetData>
@@ -16262,12 +16262,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.1796875" customWidth="1"/>
+    <col min="1" max="1" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>181</v>
       </c>
@@ -16275,12 +16275,12 @@
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>182</v>
       </c>
       <c r="B2">
-        <v>2.5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/elec/GBSC/Grid Battery Storage Capacities.xlsx
+++ b/InputData/elec/GBSC/Grid Battery Storage Capacities.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28221"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29103"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\GBSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{8CEC742D-2BD5-4C3C-8245-550944F0C0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD7E02D3-ECA8-46D3-A458-0540CE2B89CA}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{8CEC742D-2BD5-4C3C-8245-550944F0C0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B4C87FA-C847-4FA1-8A55-8A93AF231CAF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="AEO Table 9 (2019)" sheetId="8" state="hidden" r:id="rId2"/>
     <sheet name="SYGBSC" sheetId="9" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="17" r:id="rId4"/>
-    <sheet name="GBDSD" sheetId="16" r:id="rId5"/>
+    <sheet name="GBDSD" sheetId="16" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="gigwatts_to_megawatts">About!$A$33</definedName>
@@ -126,7 +125,7 @@
     <t>Start year is 2021</t>
   </si>
   <si>
-    <t>As of 2021, there were no significant grid-scale battery operations in India above that cited in 202</t>
+    <t>As of 2021, there were no significant grid-scale battery operations in India above 20 MW that is references</t>
   </si>
   <si>
     <t>ref2019.d111618a</t>
@@ -9031,15 +9030,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FA5674-5321-4209-8D92-A6FF7E3AA18C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65475C28-B52F-4DAC-B5FC-A0EDB4410349}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -9072,6 +9062,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
     <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
@@ -9215,23 +9220,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1E2A2EF-786A-4123-AAF1-8FEA655BFA2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25737437-D27D-4D3B-9BA4-D3B704ECA530}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9239,5 +9229,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25737437-D27D-4D3B-9BA4-D3B704ECA530}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1E2A2EF-786A-4123-AAF1-8FEA655BFA2D}"/>
 </file>